--- a/tests/golden/composite-review/v1/expected.xlsx
+++ b/tests/golden/composite-review/v1/expected.xlsx
@@ -1475,7 +1475,7 @@
     <t>template_digest</t>
   </si>
   <si>
-    <t>"sha256:fefe00721719b42f10cccc972c8c150c9ef92d42c2f679bbb925a833e90a0898"</t>
+    <t>"sha256:119dee00fd1e70b45e72cdb104698c5f3f50453e4424d167b981dbb22e3275ac"</t>
   </si>
   <si>
     <t>report_data_contract_version</t>
